--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,3282 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>To avoid user confusion and potential errors by ensuring a single, consistent product name is presented to the customer on 123.hp.com, as having multiple names for the same reference is inefficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-031</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Support for Consumer, SMB, and Enterprise Segments: Design solutions, services, and business models to address needs of consumer, SMB, and enterprise markets.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports diverse customer requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Solutions and services available and validated for each segment at launch.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Solutions and services available and validated for each segment at launch.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports diverse customer requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-032</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SMB Manageability and Enterprise Support: Include SMB manageability and enterprise support features such as WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Meets IT requirements for business customers and enhances manageability.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Manageability features functional and validated in enterprise test environments.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Manageability features functional and validated in enterprise test environments.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Meets IT requirements for business customers and enhances manageability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-033</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers: Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Supports wide range of deployment scenarios and user environments.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All clients and drivers pass compatibility and installation tests.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All clients and drivers pass compatibility and installation tests.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Supports wide range of deployment scenarios and user environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-037</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magellan solution</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product: Leverage Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) for new Magellan solution.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Platform integration validated in system tests.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Platform integration validated in system tests.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-038</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks: Integrate CISS IDS, NOA-F, and ink tanks into the new product platform.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports modern CISS features and improves product competitiveness.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>All components function as integrated system in validation tests.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>All components function as integrated system in validation tests.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Supports modern CISS features and improves product competitiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-039</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>New NGB Keyed Ink Bottles: Develop new NGB keyed ink bottles for the platform.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-041</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SuperAmp</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K as Constrained Priority: Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a constrained program requirement.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Critical for warranty, reliability, and cost targets.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing for 65,000 pages with &lt;1% failure rate.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA achieves a minimum life of 65,000 pages with &lt;1% failure rate.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Critical for warranty, reliability, and cost targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-042</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years and 80,000 Pages as Optimized Priority: Optimize for warranty life of 2 years and 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Meets customer expectations for durability and value.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Product passes reliability testing for 2 years/80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Warranty life of 2 years and 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Meets customer expectations for durability and value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-043</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority: Optimize for print throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Competitive performance metric for target market.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Printer achieves rated throughput of 25/20 ppm in standard performance tests.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Competitive performance metric for target market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-044</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box) as Optimized Priority: Optimize serviceability, focusing on maintenance box accessibility and replacement.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Reduces service time and improves customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Maintenance box is replaceable within defined service time.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maintenance box is easily replaceable by the customer within a defined service time.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Reduces service time and improves customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-047</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Business Leadership</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priority: Host 12,000-page CMYK and trade page 6,000 as flexible priorities for the program.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Provides flexibility for future product enhancements or market demands.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12K-CMYK and 6K trade page features can be enabled as needed.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>The architecture supports enabling 12K CMYK and 6K trade page yields.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Provides flexibility for future product enhancements or market demands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>User testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>High Serviceability and Customer Replaceable Parts: Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management: Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Wong, Rahul1, Ming</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles for Error Prevention: Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>&lt;2% incorrect refill incidents over 12 months of use.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui, Parvin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Advanced View SMB Portal: Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Parvin, Rahul1, Shin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Marketing, DVAR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PDL/PS Support and Improved Print Speed: For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Parvin, Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AI Solutions for Print, Scan, and Support: Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Reduce manual steps by at least 30% in key workflows.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Bottles must be validated to deliver at least 6,000 pages for Black and CMY.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Black: 6,000 pages; CMY: &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure all ink bottles and refilling processes are spill-free to enhance reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 99% of refilling scenarios during reliability testing.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>100% spill-free refilling.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NOA-F must pass validation with new labyrinth and lid label while maintaining existing functional interfaces.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pass validation with new components while maintaining existing functional interfaces.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks: Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new platform.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks must meet all print quality and reliability standards in Magellan platform.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Meet all print quality and reliability standards in Magellan platform.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Characterization Modeling: Characterize and model reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) parameters.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ensures system robustness, longevity, and supports warranty claims.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Models must be validated and predictive within +/-10% of observed reliability outcomes in pilot runs.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Models predictive within +/-10% of observed reliability outcomes.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in tanks and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ensures long-term print quality and reduces field failures.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ink stability modeling must predict PQ impact over 2-year warranty life with &lt;5% deviation from field data.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Predict PQ impact with &lt;5% deviation.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ensures long-term print quality and reduces field failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support: Provide NOA-F as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NOA-F service parts available and replaceable within warranty support SLAs.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Available and replaceable within warranty support SLAs.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the ink bottle lid for improved traceability or anti-counterfeiting.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Enhances product security and traceability in the supply chain.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Acumen 6 features must be verifiable on all production lids and pass security audits.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Verifiable on all production lids and pass security audits.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Enhances product security and traceability in the supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SA14 and Orcus 5 lines operational with new components and pass production validation.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Lines operational and pass production validation.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design PHA and NOA-F to be customer replaceable, enhancing serviceability.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F using provided instructions with &lt;5% error rate in usability tests.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>&lt;5% error rate in usability tests.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>New Warranty Page Life Goal of 80,000 Pages: Set new warranty page life goal for the printer at 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aligns with market expectations for durability and reduces TCO for customers.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Printer must operate without critical failure for at least 80,000 pages in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>80,000 pages page life</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Product Reddington ID with Increased Tank Size: Adopt Reddington ID for product with increased tank size, while keeping Marconi-HI ADF unchanged.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Product ID and tank design validated in pilot production; ADF remains unchanged.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Adopt Reddington ID for product with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the product.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Improves product protection during shipping and handling.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>EPS foam packaging passes ISTA transit and drop tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for product protection.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Improves product protection during shipping and handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion: Modify input and output trays to align with new tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank in user tests and fit within defined product envelope.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Modified input and output trays to align with new tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>REQ-016</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display: Integrate a 4.3” CGD (Color Graphic Display) into the product.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Enhances user interface and usability.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Display is functional, clear, and passes user experience tests.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3” CGD.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Enhances user interface and usability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>REQ-017</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with New Routing and Integration: Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Supports increased ink flow and reliability with new tank design.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>New routing and integration validated in reliability and flow tests.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Develop new tube routing and integration for a 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Supports increased ink flow and reliability with new tank design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>REQ-018</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Update service station for improved aerosol management and adapt platform for tank changes.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Reduces maintenance and improves print environment cleanliness.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within safety thresholds during operation.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Improved aerosol management in service station.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Reduces maintenance and improves print environment cleanliness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REQ-019</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Carriage operates reliably and meets print quality standards in system tests.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REQ-020</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Paperpath Support for Increased Page Life: Update paperpath design to support increased 80,000-page life goal.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability over extended use.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Paperpath passes accelerated life testing for 80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Paperpath supports 80,000-page life.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REQ-021</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Extends product life and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part within standard service time.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part within standard service time.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Extends product life and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REQ-022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Introduce 140ml black bottles and new, larger CMY bottles for the ink system.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Bottles validated for compatibility and yield in system tests.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bottles validated for compatibility and yield in system tests.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>REQ-023</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Quality</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Develop new make-break and FI (fluidic interconnect) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and mis-fill prevention tests.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and mis-fill prevention tests.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>REQ-024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Implement new IDS startup algorithm and air management system.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Startup and air management pass reliability and air ingress tests.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Startup and air management pass reliability and air ingress tests.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>REQ-025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Develop new algorithms for servicing and startup to support new platform requirements.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Improves reliability and user experience with new system components.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Improves reliability and user experience with new system components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>REQ-026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Set new print quality (PQ) goals and depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ensures consistent output quality and accurate yield metrics.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics validated in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics validated in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ensures consistent output quality and accurate yield metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>REQ-027</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R&amp;D, Supply</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new platform.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware to reduce development cost and risk.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Hardware passes system integration and functional validation.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Hardware passes system integration and functional validation.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware to reduce development cost and risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>REQ-028</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Provides modern connectivity options for users.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Provides modern connectivity options for users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>REQ-029</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>R&amp;D, Firmware, Product Management</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Utilize Dune firmware platform for the printer.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Firmware passes system and feature validation tests.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Firmware passes system and feature validation tests.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>REQ-030</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IT, Security, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Meets enterprise security requirements and protects user data.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance tests.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance tests.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Meets enterprise security requirements and protects user data.</t>
         </is>
       </c>
     </row>
@@ -571,7 +3847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +4199,626 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold/Target are not specific or measurable. 'Meet customer requirement' is too vague and does not provide an actionable, measurable metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-034</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hui</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Protect Micro/SMB Segments and HP's Ink/Laser Profit Pool: Design product features and pricing to protect HP's micro/SMB segments and profit pool from competitors.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Strategic business objective to maintain market share and profitability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Market share and profit pool metrics maintained post-launch.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Market share and profit pool metrics improved post-launch.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a high-level business strategy, not a specific and actionable product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-035</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lead with LaserJet, Flank with PDL in Medium and Enterprise Segments: Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments to win over competitors like Epson as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a marketing strategy, not a specific and actionable product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-036</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Grow Profitable CISS Share in New Segments: Expand CISS offerings to new segments to grow HP's profitable market share.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Increases revenue and market penetration.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CISS share in new segments increases post-launch.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CISS share in new segments increases post-launch.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a high-level business objective, not a specific and actionable product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-040</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Program Management</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Documentation and Process</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schedule as Constrained Priority: Adhere to schedule as the least flexible business constraint for the program.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ensures timely market entry and supports business objectives.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>All key milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>All key milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Do not include best practices or general engineering/process standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-045</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SMB Solution as Optimized Priority: Optimize product features and solutions for SMB market needs.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Increases product adoption and satisfaction in SMB segment.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SMB features validated in customer pilots and feedback.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Product features and solutions are optimized for SMB market needs.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not measurable or specific. Acceptance criteria 'validated in customer pilots and feedback' lacks a specific metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-046</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, IT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, IT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) as Optimized Priority: Optimize for PaaS business model and schedule.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Enables new revenue streams and flexible deployment.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PaaS features operational and validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PaaS features are operational and validated.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not measurable or specific. Acceptance criteria 'validated in pilot deployments' lacks a specific metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement threshold must be specific and actionable, not relative to previous generations ('10% lower than previous HP SMB products').</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability Thresholds: Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Warranty of 80,000 pages or 2 years (whichever comes first). Warranty terms published and service processes validated before launch.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>80,000 pages or 2 years</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requests for Warranty Improvement must be routed to Function owners (Marketing/GxD/TME) for holistic assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Maintenance-Free or Low Maintenance Design: Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>at least 30% lower than comparable products</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement threshold/target must be specific and actionable, not relative to 'comparable products'.</t>
         </is>
       </c>
     </row>
@@ -937,9 +4833,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Achieve EPEAT3, LOT4, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ming, Lim, Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Blue Angel Environmental Certification: Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Blue Angel certification awarded by launch date.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Blue Angel certification awarded by launch date.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ming, Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>High Recycled Content in Plastics (60% RCP): Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>≥60% RCP in plastics</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,3690 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>To avoid user confusion and potential errors by ensuring a single, consistent product name is presented to the customer on 123.hp.com, as having multiple names for the same reference is inefficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-031</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Support for Consumer, SMB, and Enterprise Segments: Design solutions, services, and business models to address needs of consumer, SMB, and enterprise markets.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports diverse customer requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Solutions and services available and validated for each segment at launch.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Solutions and services available and validated for each segment at launch.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports diverse customer requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-032</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SMB Manageability and Enterprise Support: Include SMB manageability and enterprise support features such as WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Meets IT requirements for business customers and enhances manageability.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Manageability features functional and validated in enterprise test environments.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Manageability features functional and validated in enterprise test environments.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Meets IT requirements for business customers and enhances manageability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-033</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers: Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Supports wide range of deployment scenarios and user environments.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All clients and drivers pass compatibility and installation tests.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All clients and drivers pass compatibility and installation tests.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Supports wide range of deployment scenarios and user environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-034</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Protect Micro/SMB Segments and HP's Ink/Laser Profit Pool: Design product features and pricing to protect HP's micro/SMB segments and profit pool from competitors.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Strategic business objective to maintain market share and profitability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Market share and profit pool metrics maintained post-launch.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Market share and profit pool metrics improved post-launch.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Strategic business objective to maintain market share and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-035</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lead with LaserJet, Flank with PDL in Medium and Enterprise Segments: Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments to win over competitors like Epson as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-036</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Grow Profitable CISS Share in New Segments: Expand CISS offerings to new segments to grow HP's profitable market share.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Increases revenue and market penetration.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CISS share in new segments increases post-launch.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CISS share in new segments increases post-launch.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Increases revenue and market penetration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-037</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Magellan solution</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product: Leverage Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) for new Magellan solution.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Platform integration validated in system tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Platform integration validated in system tests.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-038</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks: Integrate CISS IDS, NOA-F, and ink tanks into the new product platform.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Supports modern CISS features and improves product competitiveness.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>All components function as integrated system in validation tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>All components function as integrated system in validation tests.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Supports modern CISS features and improves product competitiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-039</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>New NGB Keyed Ink Bottles: Develop new NGB keyed ink bottles for the platform.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-041</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SuperAmp</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K as Constrained Priority: Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a constrained program requirement.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Critical for warranty, reliability, and cost targets.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing for 65,000 pages with &lt;1% failure rate.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA achieves a minimum life of 65,000 pages with &lt;1% failure rate.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Critical for warranty, reliability, and cost targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-042</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years and 80,000 Pages as Optimized Priority: Optimize for warranty life of 2 years and 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Meets customer expectations for durability and value.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Product passes reliability testing for 2 years/80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Warranty life of 2 years and 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Meets customer expectations for durability and value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-043</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority: Optimize for print throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Competitive performance metric for target market.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Printer achieves rated throughput of 25/20 ppm in standard performance tests.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Competitive performance metric for target market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-044</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box) as Optimized Priority: Optimize serviceability, focusing on maintenance box accessibility and replacement.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Reduces service time and improves customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Maintenance box is replaceable within defined service time.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maintenance box is easily replaceable by the customer within a defined service time.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Reduces service time and improves customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-047</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Business Leadership</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priority: Host 12,000-page CMYK and trade page 6,000 as flexible priorities for the program.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Provides flexibility for future product enhancements or market demands.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>12K-CMYK and 6K trade page features can be enabled as needed.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The architecture supports enabling 12K CMYK and 6K trade page yields.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Provides flexibility for future product enhancements or market demands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>User testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>High Serviceability and Customer Replaceable Parts: Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bottles must be validated to deliver at least 6,000 pages for Black and CMY.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Black: 6,000 pages; CMY: &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure all ink bottles and refilling processes are spill-free to enhance reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 99% of refilling scenarios during reliability testing.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>100% spill-free refilling.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NOA-F must pass validation with new labyrinth and lid label while maintaining existing functional interfaces.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pass validation with new components while maintaining existing functional interfaces.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks: Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new platform.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks must meet all print quality and reliability standards in Magellan platform.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Meet all print quality and reliability standards in Magellan platform.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Characterization Modeling: Characterize and model reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) parameters.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ensures system robustness, longevity, and supports warranty claims.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Models must be validated and predictive within +/-10% of observed reliability outcomes in pilot runs.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Models predictive within +/-10% of observed reliability outcomes.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in tanks and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Ensures long-term print quality and reduces field failures.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ink stability modeling must predict PQ impact over 2-year warranty life with &lt;5% deviation from field data.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Predict PQ impact with &lt;5% deviation.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Ensures long-term print quality and reduces field failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support: Provide NOA-F as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOA-F service parts available and replaceable within warranty support SLAs.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Available and replaceable within warranty support SLAs.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the ink bottle lid for improved traceability or anti-counterfeiting.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Enhances product security and traceability in the supply chain.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Acumen 6 features must be verifiable on all production lids and pass security audits.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Verifiable on all production lids and pass security audits.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Enhances product security and traceability in the supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SA14 and Orcus 5 lines operational with new components and pass production validation.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Lines operational and pass production validation.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design PHA and NOA-F to be customer replaceable, enhancing serviceability.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F using provided instructions with &lt;5% error rate in usability tests.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>&lt;5% error rate in usability tests.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>New Warranty Page Life Goal of 80,000 Pages: Set new warranty page life goal for the printer at 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Aligns with market expectations for durability and reduces TCO for customers.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Printer must operate without critical failure for at least 80,000 pages in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>80,000 pages page life</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Product Reddington ID with Increased Tank Size: Adopt Reddington ID for product with increased tank size, while keeping Marconi-HI ADF unchanged.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Product ID and tank design validated in pilot production; ADF remains unchanged.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Adopt Reddington ID for product with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the product.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Improves product protection during shipping and handling.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>EPS foam packaging passes ISTA transit and drop tests.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for product protection.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Improves product protection during shipping and handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion: Modify input and output trays to align with new tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank in user tests and fit within defined product envelope.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Modified input and output trays to align with new tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>REQ-016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display: Integrate a 4.3” CGD (Color Graphic Display) into the product.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Enhances user interface and usability.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Display is functional, clear, and passes user experience tests.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3” CGD.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Enhances user interface and usability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REQ-017</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with New Routing and Integration: Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Supports increased ink flow and reliability with new tank design.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>New routing and integration validated in reliability and flow tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Develop new tube routing and integration for a 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Supports increased ink flow and reliability with new tank design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>REQ-018</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Update service station for improved aerosol management and adapt platform for tank changes.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Reduces maintenance and improves print environment cleanliness.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within safety thresholds during operation.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Improved aerosol management in service station.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Reduces maintenance and improves print environment cleanliness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>REQ-019</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Carriage operates reliably and meets print quality standards in system tests.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>REQ-020</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paperpath Support for Increased Page Life: Update paperpath design to support increased 80,000-page life goal.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability over extended use.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Paperpath passes accelerated life testing for 80,000 pages without critical failure.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Paperpath supports 80,000-page life.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope as per PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>REQ-021</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Extends product life and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part within standard service time.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance part within standard service time.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Extends product life and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REQ-022</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Introduce 140ml black bottles and new, larger CMY bottles for the ink system.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Bottles validated for compatibility and yield in system tests.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bottles validated for compatibility and yield in system tests.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REQ-023</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Quality</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Develop new make-break and FI (fluidic interconnect) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and mis-fill prevention tests.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and mis-fill prevention tests.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REQ-024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Implement new IDS startup algorithm and air management system.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Startup and air management pass reliability and air ingress tests.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Startup and air management pass reliability and air ingress tests.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REQ-025</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Develop new algorithms for servicing and startup to support new platform requirements.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Improves reliability and user experience with new system components.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Improves reliability and user experience with new system components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>REQ-026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Product Management</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Set new print quality (PQ) goals and depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Ensures consistent output quality and accurate yield metrics.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics validated in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics validated in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Ensures consistent output quality and accurate yield metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>REQ-027</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R&amp;D, Supply</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new platform.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware to reduce development cost and risk.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Hardware passes system integration and functional validation.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Hardware passes system integration and functional validation.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware to reduce development cost and risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>REQ-028</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Provides modern connectivity options for users.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity and performance tests.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Provides modern connectivity options for users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>REQ-029</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>R&amp;D, Firmware, Product Management</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Utilize Dune firmware platform for the printer.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Firmware passes system and feature validation tests.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Firmware passes system and feature validation tests.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>REQ-030</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IT, Security, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Meets enterprise security requirements and protects user data.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance tests.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Security features pass penetration and compliance tests.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Meets enterprise security requirements and protects user data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management: Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles for Error Prevention: Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Reduces service incidents and improves user experience for non-technical users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Advanced View SMB Portal: Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PDL/PS Support and Improved Print Speed: For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>High Recycled Content in Plastics (60% RCP): Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AI Solutions for Print, Scan, and Support: Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability Thresholds: Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Warranty terms published and service processes validated before launch.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Provide a warranty of 80,000 pages or 2 years (whichever comes first).</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Maintenance-Free or Low Maintenance Design: Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Maintenance requirements are at least 30% lower than comparable products.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
         </is>
       </c>
     </row>
@@ -571,7 +4255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +4607,278 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold/Target are not specific or measurable. 'Meet customer requirement' is too vague and does not provide an actionable, measurable metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-040</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schedule as Constrained Priority: Adhere to schedule as the least flexible business constraint for the program.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures timely market entry and supports business objectives.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>All key milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>All key milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Do not include best practices or general engineering/process standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-045</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SMB Solution as Optimized Priority: Optimize product features and solutions for SMB market needs.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Increases product adoption and satisfaction in SMB segment.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SMB features validated in customer pilots and feedback.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Product features and solutions are optimized for SMB market needs.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not measurable or specific. Acceptance criteria 'validated in customer pilots and feedback' lacks a specific metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-046</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, IT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Product Management, Business Leadership, IT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) as Optimized Priority: Optimize for PaaS business model and schedule.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enables new revenue streams and flexible deployment.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PaaS features operational and validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PaaS features are operational and validated.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not measurable or specific. Acceptance criteria 'validated in pilot deployments' lacks a specific metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Hui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement threshold must be specific and actionable, not relative to previous generations ('10% lower than previous HP SMB products').</t>
         </is>
       </c>
     </row>
@@ -937,9 +4893,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Achieve EPEAT3, LOT4, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Blue Angel Environmental Certification: Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Blue Angel certification awarded by launch date.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Blue Angel certification awarded by launch date.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>GXD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -531,7 +531,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,12 +556,16 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>inscope</t>
+          <t>IN_SCOPE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Having multiple names for the same product (e.g., HP OJP 9010 series, 9010e series, 9010) is inefficient and can cause user errors and confusion on customer-facing platforms like 123.hp.com.</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
     </row>
@@ -572,292 +580,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Durability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Category 'Reliability' is classified as 'HW Reliability' which is Out of Scope (Common Across All Products). Additionally, the Threshold/Target 'Meet customer requirement' is not specific and measurable, violating Redefine Guidelines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>robustness</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Violated: Category 'Reliability' is classified as 'HW Reliability' which is Out of Scope (Common Across All Products). Additionally, the Threshold/Target 'Meet customer requirement' is not specific and measurable, violating Redefine Guidelines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Put printer on trolley and print</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - The Threshold/Target 'Meet customer requirement' is not specific and measurable.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -868,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -954,7 +679,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1009,7 +734,217 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The printer must meet intervention specifications for various media types and climatic conditions to ensure reliable performance across different markets.</t>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Put printer on trolley and print</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,2742 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: The printer must integrate advanced AI-driven productivity features, scan workflow enhancements, and manageability solutions to ease business operations for SMBs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Addresses the core value proposition of making business management easier for SMBs and differentiates from competitors.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Demonstrated AI productivity features in print and scan workflows; end-user can manage devices through provided solutions; meets user scenario tests.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Advanced AI-driven productivity features, scan workflow enhancements, and manageability solutions are fully integrated and validated.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Addresses the core value proposition of making business management easier for SMBs and differentiates from competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO: The printer must deliver the lowest total cost of ownership (TCO) for SMB customers compared to HP's other business printers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Independent TCO analysis demonstrates lowest TCO among HP business printers for target use-case (AMPV ~500 pages/month).</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Lowest TCO among HP business printers for target use-case.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box: The printer must feature a maintenance box that can be replaced by customers without technical assistance, with service center fallback if needed.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>User can replace maintenance box following provided instructions; no tools or minimal tools required; validated in usability testing.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Customer can replace maintenance box in under 5 minutes with no tools.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: The printer must use keyed ink bottles to prevent incorrect refilling and ensure user safety and product reliability.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Prevents user error and damage, supports warranty claims, and enhances customer experience.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Only correct ink bottle fits and dispenses; passes misfill prevention tests.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Only correct ink bottle fits and dispenses; passes misfill prevention tests.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Prevents user error and damage, supports warranty claims, and enhances customer experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management: A consolidated web-based portal must be provided for SMBs to manage and monitor their fleet of printers, tailored for non-IT users.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Enables SMBs to self-manage devices without dedicated IT staff, reducing support costs.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Portal is accessible, user-friendly, supports core management tasks (status, configuration, alerts) for 6-15 printers.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A seamless, intuitive portal for managing a fleet of 6-15 printers by non-IT users.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Enables SMBs to self-manage devices without dedicated IT staff, reducing support costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) Support: The printer and associated software must support integration with HP's PaaS offerings for enhanced solutions and services.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports HP's goal for PaaS acceleration and coverage; enables future solution monetization.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Printer can be registered and managed via HP's PaaS platform; integration validated in end-to-end tests.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full integration with HP's PaaS platform, enabling all relevant services.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports HP's goal for PaaS acceleration and coverage; enables future solution monetization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PDL/PS Support and Improved Print Speed: For PDL SKU, the printer must support PDL/PS and achieve print speeds of at least 25/20 ppm (improved from current 25/19).</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Meets business productivity needs and competitive benchmarks for print speed and compatibility.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PDL/PS compatibility verified; print speed meets or exceeds 25/20 ppm in standard test scenarios.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Print speed of at least 25/20 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Meets business productivity needs and competitive benchmarks for print speed and compatibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan AI Solutions: The printer must feature AI-powered solutions for optimizing print quality and scan accuracy, branded as Perfect Print and Perfect Scan.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Addresses top customer needs for quality and efficiency; supports key differentiator claims.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Demonstrated improvement in print/scan quality in benchmark tests; feature accessible via UI/portal.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>AI-powered solutions deliver demonstrable and marketable improvements in print and scan quality.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Addresses top customer needs for quality and efficiency; supports key differentiator claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: The printer must include a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMB customers and supports reliability claims.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Warranty terms published; support system configured to track both criteria.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Warranty covering 80,000 pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMB customers and supports reliability claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Printer must support mobile printing via HP App and standard mobile platforms.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Addresses evolving work patterns and customer expectations for mobility.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Printer discoverable and usable from HP App and mobile OS print dialogs; passes connectivity and print tests from mobile devices.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Support mobile printing via HP App and standard mobile platforms.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Addresses evolving work patterns and customer expectations for mobility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1 Shin, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Printer must support telemetry data collection for fleet management, diagnostics, and usage analytics.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Enables proactive support, device management, and product improvement.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, securely transmitted, and accessible via management portal; passes privacy and compliance review.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Support telemetry data collection for fleet management, diagnostics, and usage analytics.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Enables proactive support, device management, and product improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Develop NGB keyed ink bottles with 6,000-page yield for Black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Higher page yields reduce customer intervention and lower total cost of ownership, supporting competitive differentiation.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bottles must deliver at least 6,000 pages for Black and CMY, and CMY bottle size must exceed 8,000 pages as validated by ISO testing.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6,000-page yield for Black and CMY, CMY bottle size supporting over 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Higher page yields reduce customer intervention and lower total cost of ownership, supporting competitive differentiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>End Users, Service, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Bottles: Design ink bottles and system to ensure spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Minimizes mess and waste, improving customer satisfaction and reducing service costs.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No ink spillage occurs during standard refill process in usability and reliability testing.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Minimizes mess and waste, improving customer satisfaction and reducing service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Security, Service</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Implement NOA-F (Non-Original Accessory-Filter) with a metal foiled labyrinth and lid label, with no changes to click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Enhances security, anti-counterfeit, and operational reliability.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NOA-F must pass security validation and function seamlessly with existing mechanisms.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Implement NOA-F with metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Enhances security, anti-counterfeit, and operational reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Support for Customer Replaceable PHA and NOA-F: Enable customer replacement of Print Head Assembly (PHA) and NOA-F parts to enhance serviceability.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F without tools, as verified by usability studies.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Customer can replace PHA and NOA-F without tools.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Product Management, Service, End Users</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>New Warranty Page Life Goal of 80k Pages: Design product to support a new warranty page life goal of 80,000 pages per device.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Aligns with competitive benchmarks and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Device passes accelerated life tests simulating 80,000 printed pages without major failure.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Product life supports 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Aligns with competitive benchmarks and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Industrial Design, End Users</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Size Optimization for Larger Tank: Increase tank size to support higher ink capacity, with associated changes to input and output trays to accommodate tank protrusion.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Supports higher page yield and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Printer footprint remains within specified dimensions while supporting larger tank and functional trays.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Increase tank size while maintaining printer footprint and tray functionality.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Supports higher page yield and reduces refill frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4.3” CGD Touchscreen Interface: Integrate a 4.3-inch color graphical display (CGD) touchscreen for improved user interface.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Enhances usability and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>All key functions accessible via the 4.3” touchscreen, validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>All key functions accessible via the 4.3” touchscreen, validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Enhances usability and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement aerosol management in the service station with platform changes due to larger tank.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Prevents ink aerosol contamination and maintains print quality and reliability.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within acceptable limits during maintenance cycles.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Aerosol levels remain within acceptable limits during maintenance cycles.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Prevents ink aerosol contamination and maintains print quality and reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Redesign paper path components to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability over the extended warranty period.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Paper path components pass durability testing for 80,000 pages without failure.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Paper path components achieve 80,000 pages page life without failure.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability over the extended warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REQ-010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ink Maintenance as Serviceable Part Post-80k Life: Design ink maintenance components to be serviceable after 80,000-page life, available at service centers.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Extends device life beyond warranty and reduces e-waste.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance parts post-warranty, as validated by service documentation.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ink maintenance components are modular and replaceable by service centers post-warranty.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Extends device life beyond warranty and reduces e-waste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>New IDS Make-break and FI Connection: Develop new IDS (Ink Delivery System) make-break and fluidic interconnect (FI) connection with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Supports new tank design and ensures secure, reliable ink delivery.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>IDS connections pass leak and connectivity tests for all supported configurations.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>IDS connections pass leak and connectivity tests for all supported configurations.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Supports new tank design and ensures secure, reliable ink delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Implement a new IDS startup algorithm and air management system for optimized priming and reliability.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Improves first-time setup experience and reduces startup failures.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Startup algorithm completes successfully in 99% of new device installations.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Startup algorithm completes successfully in 99% of new device installations.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Improves first-time setup experience and reduces startup failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REQ-013</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics: Define and implement new print quality (PQ) goals and depletion metrics to align with page yield definition.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ensures consistent output and aligns with marketing claims.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Print quality and depletion meet or exceed defined metrics in 95% of test runs.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Print quality and depletion meet or exceed defined metrics in 95% of test runs.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ensures consistent output and aligns with marketing claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam for product packaging to improve protection during shipping.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Reduces damage during transit and supports logistics requirements.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Reduces damage during transit and supports logistics requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-016</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Support for SMB, Consumer, and Enterprise Services: Provide solutions and business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker options.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Expands market reach and offers flexible service models.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Service options are available and functional for all target segments at launch.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Service options are available and functional for all target segments at launch.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Expands market reach and offers flexible service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REQ-027</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SuperAmp</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint): Design SuperAmp PHA to support a life of 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sets a boundary for PHA durability and impacts service strategy.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes durability tests for 65,000 pages in accelerated testing.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Sets a boundary for PHA durability and impacts service strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>REQ-028</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Support Experience</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or Page Target: Product warranty to cover 2 years or the specified page life, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aligns with industry norms and customer expectations.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Warranty documentation clearly states coverage terms and is validated by legal and service teams.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2 years or specified page life</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Aligns with industry norms and customer expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>REQ-029</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>All, PDL variant</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm): Printer must achieve a throughput of 25/20 pages per minute (ppm), with PDL variant achieving 25/19 ppm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Meets competitive benchmarks for speed.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>25/20 ppm (25/19 ppm for PDL variant) in ISO speed tests</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>25/20 ppm (25/19 ppm for PDL variant)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Meets competitive benchmarks for speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>REQ-030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box: Ensure printer includes a serviceable maintenance box for ink waste and maintenance cycles.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces service intervention frequency.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by service personnel within 10 minutes as validated by service testing.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Serviceable maintenance box, replaceable within 10 minutes by service personnel.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces service intervention frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>REQ-017</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scan Solution and SMB Manageability: Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Meets needs of SMB and enterprise customers for device management and workflow integration.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Device supports scan and management features as validated by functional testing.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Device supports scan and management features as validated by functional testing.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Meets needs of SMB and enterprise customers for device management and workflow integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REQ-018</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OS support</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients and Drivers: Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad deployment.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Supports diverse customer IT environments and simplifies deployment.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Device installs and operates with all listed clients and drivers in supported OS environments.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Device installs and operates with all listed clients and drivers in supported OS environments.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Supports diverse customer IT environments and simplifies deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>REQ-019</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar Tubes with New Routing: Utilize Sayan Sibstar tubes for ink delivery, with new routing and integration for the 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Improves ink delivery reliability and supports new tank design.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ink delivery system operates without leaks or flow interruptions in all test scenarios.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ink delivery system operates without leaks or flow interruptions in all test scenarios.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Improves ink delivery reliability and supports new tank design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>REQ-020</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Factory Configuration for NOA-F, Magi and Nessie Ink Cart, and Labelling Tool: Modify existing factory line SA14 for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ensures efficient manufacturing and supports new product features.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Factory lines are updated and validated for new production requirements before mass production.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Factory lines are updated and validated for new production requirements before mass production.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Ensures efficient manufacturing and supports new product features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>REQ-021</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Support for SuperAmp PHA, Magi, and Nessie Pigment Inks: Ensure product supports SuperAmp PHA, Magi, and Nessie pigment inks with new 140ml K bottles and new CMY bottles.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Maintains ink compatibility and supports high yield requirements.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Device operates reliably with all specified inks and bottle sizes.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Device operates reliably with all specified inks and bottle sizes.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Maintains ink compatibility and supports high yield requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>REQ-022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Hi PDL and Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components for cost and time savings.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Reduces development cost and time by reusing proven components.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>All reused components pass functional and integration testing in new product.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>All reused components pass functional and integration testing in new product.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Reduces development cost and time by reusing proven components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REQ-023</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity requirements for all customer segments.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Device connects to Wi-Fi networks using Stingray module in all supported regions.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Device connects to Wi-Fi networks using Stingray module in all supported regions.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity requirements for all customer segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REQ-024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>OS support</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Firmware (FW) Dune Platform: Utilize Dune firmware platform for device operation and feature support.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ensures consistent firmware experience and supports new hardware features.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Device operates reliably with Dune firmware and supports all required features.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Device operates reliably with Dune firmware and supports all required features.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Ensures consistent firmware experience and supports new hardware features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REQ-025</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features for both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Protects against unauthorized access and enhances device security posture.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Device passes HP security certification for Gauss4.xx features.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Device passes HP security certification for Gauss4.xx features.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Protects against unauthorized access and enhances device security posture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REQ-026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Program Management</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schedule Adherence (Q3'25-Q4'27): Meet program schedule with key checkpoints from Q3'25 to Q4'27 as detailed in project plan.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ensures timely market entry and aligns with business objectives.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>All program milestones are completed on or before scheduled dates.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>All program milestones are completed on or before scheduled dates.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a general process guideline (project schedule), not a customer-facing product feature.</t>
         </is>
       </c>
     </row>
@@ -580,9 +3316,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-011</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Maintenance Free or Less Maintenance Design: Design the printer to be maintenance free or require less maintenance (i.e., fewer parts to replace over product lifetime).</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Reduces burden on SMBs with limited technical resources and aligns with competitor differentiation.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Product requires fewer maintenance interventions than comparable models; validated by field test data.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Maintenance free or less maintenance design.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold is not specific and measurable (references 'comparable models').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +3825,218 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Environment &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Relevant SKU for Blue Angel</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification: The printer must meet Blue Angel environmental certification requirements for the relevant SKU.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Supports sustainability goals and competitive positioning, particularly in regulated markets.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Certification documentation received; product listed as Blue Angel compliant.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Achieve Blue Angel certification for the relevant SKU.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Supports sustainability goals and competitive positioning, particularly in regulated markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environment &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>60% Recycled Content Plastic (RCP): Printer must utilize at least 60% recycled content plastic in its construction, exceeding key competitor benchmarks (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and supports marketing claims.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BOM and supplier documentation confirm 60% RCP; validated by internal audit.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Utilize at least 60% recycled content plastic in construction.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Differentiates HP on sustainability and supports marketing claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-014</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU: Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports environmental sustainability goals and required certifications for market access.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Product passes third-party certification for EPEAT3, LOT4, and Blue Angel.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Achieve EPEAT3, LOT4, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports environmental sustainability goals and required certifications for market access.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -556,16 +556,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IN_SCOPE</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Having too many product names for the same reference is inefficient and can induce user errors, negatively impacting the customer experience.</t>
         </is>
       </c>
     </row>
@@ -580,9 +576,292 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Put printer on trolley and print</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,216 +1014,6 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Durability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Put printer on trolley and print</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GXD</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -561,7 +561,11 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Having too many product names for the same reference is inefficient and can induce user errors, negatively impacting the customer experience.</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
     </row>
@@ -662,7 +666,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -677,7 +681,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Durability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -717,7 +721,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer requirement ') is not specific and measurable.</t>
         </is>
       </c>
     </row>
@@ -732,7 +736,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -787,7 +791,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
         </is>
       </c>
     </row>
@@ -802,7 +806,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -817,7 +821,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Print Quality</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -857,7 +861,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Requirement thresholds/targets must be specific and measurable, not vague statements like 'Meet customer requirement'.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
         </is>
       </c>
     </row>
@@ -958,7 +962,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>GXD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -531,11 +531,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Having multiple names for the same product (e.g., HP OJP 9010 series, 9010e series, 9010 All-in-One) is inefficient and can cause user confusion and errors.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -580,292 +576,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Durability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer requirement ') is not specific and measurable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HDRV</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Put printer on trolley and print</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -876,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,7 +675,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -992,32 +705,242 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>To ensure the printer meets intervention specifications and maintains print quality across different media and climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>robustness</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To prevent a known hardware failure (broken input tray sensor flag) that occurred in a predecessor product (Vasari) when placed on uneven surfaces.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>extended supporting document</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To assess for functional failure if a customer tilts the printer (e.g., 20 degrees) during printing.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Put printer on trolley and print</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>To verify that print quality is not negatively impacted when the printer is operated on an unstable or moving surface, like a trolley.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GXD</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -531,7 +531,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Having multiple names for the same product (e.g., HP OJP 9010 series, 9010e series, 9010 All-in-One) is inefficient and can cause user confusion and errors.</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -576,9 +580,292 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer requirement ') is not specific and measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Put printer on trolley and print</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -589,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +962,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -705,7 +992,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>To ensure the printer meets intervention specifications and maintains print quality across different media and climatic conditions for the Manhattan platform.</t>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,216 +1018,6 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>robustness</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>To prevent a known hardware failure (broken input tray sensor flag) that occurred in a predecessor product (Vasari) when placed on uneven surfaces.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To assess for functional failure if a customer tilts the printer (e.g., 20 degrees) during printing.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Put printer on trolley and print</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>To verify that print quality is not negatively impacted when the printer is operated on an unstable or moving surface, like a trolley.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>GXD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer requirement ') is not specific and measurable.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target ('Meet customer  requirement ') is not specific and measurable.</t>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,3066 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product Management, QA, End Users</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IT Security, Compliance, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams. Warranty is 80k pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features implemented.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Active and secure telemetry transmitting key metrics for usage, performance, and errors, accessible to support/engineering.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Seamless integration with HP App on iOS/Android for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6,000 pages for black, 6,000 pages for CMY, and CMY bottle size &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Lim</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Security &amp; Privacy, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>All NOA-F units pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>The new printer operates reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Customer-replaceable PHA and NOA-F; parts available for warranty service.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>All bottles have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ops (Inferred)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ops (Inferred)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Validated production lines at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal process (Design for Manufacturing), not a customer-facing product feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Delivered and validated mold tools for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal process/investment (tooling), not a customer-facing product feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>17</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing or product-specific feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PDL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
         </is>
       </c>
     </row>
@@ -580,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +3922,208 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Technical and business model enablement for monetization of AI and management solutions.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business/strategic goal (monetization) rather than a product-specific feature. Should be routed to the correct forum for business planning.</t>
         </is>
       </c>
     </row>
@@ -876,7 +4138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +4283,336 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Models predict at least 95% uptime and consistent PQ over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GXD</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Performance/Feature</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>robustness</t>
+          <t>Robustness</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -635,77 +635,147 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target is not specific ('Meet customer requirement'). It must be specific, actionable, and measurable.</t>
+          <t>Violated: Redefine Guideline - Requirement threshold/target must be specific and must not be vague like 'Meet customer requirement'.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tilt left and right each while printing</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule - Category 'HW Reliability' is Out of Scope and managed via Extended Supporting Documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>5</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Chong, Shin</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HDRV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Legacy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Quality Improvement &amp; Serviceability</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Print Quality</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Put printer on trolley and print</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>OUT_OF_SCOPE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold/Target is not specific ('Meet customer requirement'). It must be specific, actionable, and measurable.</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement threshold/target must be specific and must not be vague like 'Meet customer requirement'.</t>
         </is>
       </c>
     </row>
@@ -733,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,7 +889,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -834,7 +904,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Media Support</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -875,76 +945,6 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chong, Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Legacy</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>robustness</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Tilt left and right each while printing</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,6 +776,3346 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Requirement threshold/target must be specific and must not be vague like 'Meet customer requirement'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product Management, QA, End Users</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IT Security, Compliance, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>42</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Product Management, Service, Channel Partners</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PaaS available at launch.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Wong, Shin, Lim, Ming, Hui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched that can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500).</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available and functional.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>AI features demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Portal is live and supports management of 6-15 printers.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Portal is usable by non-IT trained staff (office managers/generalists), confirmed by usability testing.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Hui</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Achieve lowest TCO among HP business tank printers for SMBs.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Shin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Maintenance box replacement is validated by usability testing to be easy for end users.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui, Shin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1, Lim, Hui, Shin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing, Tech Reg, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ming, Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Printer uses at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>16</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>32</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>33</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>37</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>39</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>41</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Shin, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years (whichever comes first).</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Telemetry is active and securely transmits key metrics.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui, Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business model strategy, not a product-specific, customer-facing feature or improvement.</t>
         </is>
       </c>
     </row>
@@ -803,7 +4143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +4288,270 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4116,6 +4116,3144 @@
       <c r="N55" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Requirement is a business model strategy, not a product-specific, customer-facing feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>21</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>23</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>24</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Product Management, QA, End Users</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>25</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>26</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>27</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IT Security, Compliance, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>29</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>30</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>31</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>5</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>9</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>10</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams. Warranty is 80k pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features implemented.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Active and secure telemetry transmitting key metrics for usage, performance, and errors, accessible to support/engineering.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>12</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Seamless integration with HP App on iOS/Android for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>6</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>9</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>10</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>11</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>12</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>13</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>15</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>16</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>17</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>20</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>32</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>33</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>34</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>35</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>36</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>37</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>38</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>39</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>40</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>41</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
         </is>
       </c>
     </row>
@@ -4130,9 +7268,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Technical and business model enablement for monetization of AI and management solutions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business/strategic goal (monetization) rather than a product-specific feature. Should be routed to the correct forum for business planning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4143,7 +7556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4552,6 +7965,270 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,6 +776,3020 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Requirement threshold/target must be specific and must not be vague like 'Meet customer requirement'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Deliver high ROI, efficiency, and require minimal IT intervention for the target SMB segment.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Advanced AI-powered productivity, scan workflow, and printer manageability solutions (Perfect Print, Perfect Scan).</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A consolidated portal for managing multiple printers, usable by non-IT staff.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Customer-replaceable maintenance box.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Keyed ink bottles to prevent incorrect refilling.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU supports SMB2.0 Solutions, Advanced View SMB portal, and PaaS.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams. Warranty is 80k pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features implemented.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Active and secure telemetry transmitting key metrics for usage, performance, and errors, accessible to support/engineering.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Seamless integration with HP App on iOS/Android for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Achieve 6,000 pages for black and CMY, and CMY bottle size supports &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>All NOA-F units pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>The new printer operates reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA are customer-replaceable and available as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>All bottles have validated Acumen 6 feature on the lid.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Validated production lines capable of producing new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal operational process, not a customer-facing product feature. To be handled in Ops readiness forum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Mold tools for 1-4 new keyed caps delivered and pass first article inspection.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal capex/tooling item, not a customer-facing product feature. The resulting feature (keyed cap) is in scope, but the tooling is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Product passes all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>27</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
         </is>
       </c>
     </row>
@@ -790,9 +3804,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Product Management, Service, Channel Partners</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a project management task (schedule optimization), not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing, Tech Reg, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>25/20 ppm speed, PDL/PS support, and Blue Angel certification for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Requirement bundles in-scope features (print speed, PDL/PS) with an out-of-scope compliance item (Blue Angel certification). Compliance requirements should be handled separately as per 'Extended_Supporting_Documents' rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Technical and business model enablement for monetization of AI and management solutions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business/strategic goal (monetization) rather than a product-specific feature. Should be routed to the correct forum for business planning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -803,7 +4092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +4237,402 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Models predict at least 95% uptime and consistent PQ over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Classification: Requirement falls under 'Environmental/Sustainability', which is managed via an Extended Supporting Document per PRD Scope Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,2814 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Product Management, QA, End Users</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>25</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IT Security, Compliance, Enterprise Customers</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>29</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>31</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>33</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>37</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>38</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>39</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>40</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>41</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams. Warranty is 80k pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features implemented.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Active and secure telemetry transmitting key metrics for usage, performance, and errors, accessible to support/engineering.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>12</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Seamless integration with HP App on iOS/Android for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
         </is>
       </c>
     </row>
@@ -580,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +3670,538 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Requirement threshold/target must be specific. 'Meet customer requirement' is too vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Technical and business model enablement for monetization of AI and management solutions.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business/strategic goal (monetization) rather than a product-specific feature. Should be routed to the correct forum for business planning.</t>
         </is>
       </c>
     </row>
@@ -876,7 +4216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +4361,270 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,2946 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Adopt Reddington industrial design with an increased tank size.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Modified input and output trays to align with tank protrusion and optimized size.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3-inch color graphical display (CGD).</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IT Security</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>31</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>33</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>34</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>37</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>38</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>39</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>41</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Wong</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years (whichever comes first) is implemented and documented.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years (whichever comes first), with PHA and MINK serviceability features implemented and validated by service/support teams.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Telemetry is active and securely transmits key metrics.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
         </is>
       </c>
     </row>
@@ -580,7 +3520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +3802,670 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Category 'Environmental &amp; Sustainability compliance' is Out of Scope as per PRD_Scope_Rules. This is a common requirement handled via Extended Supporting Documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE: Category 'Environment &amp; Sustainability compliance' is managed via an extended supporting document process as per PRD Scope Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui, Shin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not a product-specific feature but a business/monetization strategy. Should be routed to the appropriate business forum.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>GXD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IN_SCOPE</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -566,6 +566,5790 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Adopt Reddington industrial design with an increased tank size.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Modified input and output trays to align with tank protrusion and optimized size.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3-inch color graphical display (CGD).</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IT Security</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>31</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>33</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>34</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>37</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>38</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>39</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>41</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Wong</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years (whichever comes first) is implemented and documented.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years (whichever comes first), with PHA and MINK serviceability features implemented and validated by service/support teams.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Telemetry is active and securely transmits key metrics.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Print Speed Requirements: Achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language) mode.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Printer must achieve 25 ppm (standard) and 20 ppm (PDL) in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25 ppm (standard) and 20 ppm (PDL)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Competitive print speed is essential for market positioning in SMB and enterprise segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Support a new warranty page life target of 80,000 pages for the product.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Product must meet warranty requirements for 80,000 pages printed under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Aligns with new market expectations and reduces total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington industrial design with an increased tank size, but no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ID must be approved and tank must accommodate new bottle sizes as specified.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Approved Reddington ID with increased tank size.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>15</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications: Modify input and output trays to align with tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Trays must function without interference and pass paper handling reliability tests.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Modified input and output trays aligned with tank protrusion.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Accommodates increased tank size and ensures smooth paper handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>16</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>4.3-inch CGD Display: Integrate a 4.3-inch color graphical display (CGD) on the printer.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Display must be functional and pass usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Enhances user interaction and supports advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>17</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes: Leverage Sayan Sibstar tubes with new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ink flow must meet print speed and reliability targets using new tube configuration.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes with new tube routing.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Improves ink flow and supports increased tank and page life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>20</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life: Design paper path to support increased page life target of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Paper path must pass 80,000-page reliability test with no major jams or failures.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Design paper path to support 80,000 pages page life.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Reliability of paper handling over extended life is crucial for warranty and customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>21</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part: Make ink maintenance a serviceable part, replaceable at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Service center must be able to replace ink maintenance part post-80,000 pages as per service manual.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Facilitates maintenance and extends product life beyond warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>23</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management for improved reliability and startup performance.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Printer must achieve successful startup and air purge in 99% of test cycles.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and minimizes air-related print defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>24</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>New Print Quality (PQ) Goals and Depletion Definition: Set new print quality goals and ink depletion definitions to align with page yield targets.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Product must meet defined PQ metrics and depletion points in validation tests.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations for output quality and consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>25</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new product.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>All reused components must pass full system integration and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>26</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Printer must connect to Wi-Fi and pass wireless certification tests.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features required by SMB and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>27</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security for Hardware and Firmware: Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Product must pass all HP security certification and penetration tests.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Meets HP and industry security standards for enterprise and SMB markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>29</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support: Support business models for Consumer, SMB, and Enterprise segments, including PaaS, WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>All business models and onboarding paths must be validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with HP’s strategic intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>30</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scan and SMB/Enterprise Manageability Solutions: Integrate scan solution and SMB manageability features, with enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM (Job Accounting Manager).</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>All listed manageability and scan features must be available and pass functional validation.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Enhances value proposition for business and enterprise customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>31</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients must install and function correctly on supported OS.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with HP ecosystems and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>32</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Micro/SMB Segments</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Strategic Protection of Micro/SMB Segments: Implement features and pricing to protect HP’s micro and SMB segments, safeguarding traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Market analysis shows retention or growth in micro/SMB segment after launch.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Critical for HP’s market share retention and profitability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>33</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>LaserJet, PDL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LaserJet Leadership and PDL Flanking: Lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Product launch plan aligns with strategic positioning and initial sales targets are met.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Strategic positioning to grow CISS share and compete with Epson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>34</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CISS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CISS Profitable Share Growth in New Segments: Expand CISS offerings to new profitable market segments.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Product launched in at least one new segment with positive ROI.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Drives revenue growth and leverages CISS technology investments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>37</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65,000 Pages: Set SuperAmp PHA life at 65,000 pages as a fixed constraint.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve 65,000-page life in validation testing.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Ensures consumable life aligns with system reliability and service intervals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>38</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80,000 Pages: Support warranty life of 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Warranty documentation and system must support the stated warranty terms.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>39</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PDL mode</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL): Maintain throughput of 25/20 ppm for PDL as an optimization priority.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Throughput validated at 25/20 ppm in PDL mode in system tests.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>25/20 ppm</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Maintains competitiveness in performance-sensitive segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>40</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Maintenance Box</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box): Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Maintenance box must be easily replaceable and pass serviceability tests.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability, particularly regarding the maintenance box.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Reduces service downtime and cost, improves user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>41</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SMB SKUs</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SMB Solution Optimization: Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>SMB-specific features validated with pilot customers.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Optimize product features and solutions for SMB customers.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Addresses key needs of a major target segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Printing Solution: Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal: Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Magellan has HP's lowest business TCO among SMB tank printers.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by end users without HP technician intervention.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>6</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed and only fit the correct tanks.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>7</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU Features: For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and supports new service models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>9</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>At least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>10</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Warranty and Serviceability: Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams. Warranty is 80k pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Warranty of 80k pages or 2 years, with PHA (customer replaceable) and MINK (service center) serviceability features implemented.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces SMB downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>11</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Active and secure telemetry transmitting key metrics for usage, performance, and errors, accessible to support/engineering.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>12</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Seamless integration with HP App on iOS/Android for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
         </is>
       </c>
     </row>
@@ -580,7 +6364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +6450,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -676,12 +6460,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quality Improvement &amp; Serviceability</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Durability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -716,12 +6500,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>outscope</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target is not specific ('Meet customer requirement').</t>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
         </is>
       </c>
     </row>
@@ -736,7 +6520,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -746,7 +6530,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quality Improvement &amp; Serviceability</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -786,12 +6570,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>outscope</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Violated: Redefine Guideline - Threshold/Target is not specific ('Meet customer requirement').</t>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
         </is>
       </c>
     </row>
@@ -806,7 +6590,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -816,52 +6600,1318 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Put printer on trolley and print</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold/Target must be specific and measurable. 'Meet customer requirement' is too vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Quality Improvement &amp; Serviceability</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Put printer on trolley and print</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>OUT_OF_SCOPE</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold/Target is not specific ('Meet customer requirement').</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Category 'Environmental &amp; Sustainability compliance' is Out of Scope as per PRD_Scope_Rules. This is a common requirement handled via Extended Supporting Documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE: Category 'Environment &amp; Sustainability compliance' is managed via an extended supporting document process as per PRD Scope Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui, Shin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is not a product-specific feature but a business/monetization strategy. Should be routed to the appropriate business forum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal R&amp;D process (modeling) rather than a customer-facing product feature or performance metric. It falls under 'best practices'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement pertains to factory line modifications, which is an internal operational/Capex issue, not a customer-facing product requirement. Should be handled via offline conversation with Operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a capital investment/tooling task, not a customer-facing product requirement. Should be handled as a program dependency or via offline conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>28</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance: Ensure compliance with EPEAT3, LOT4, and Blue Angel standards for environmental and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Required for market access and sustainability commitments.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Product must be certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Violated: Category 'Environment &amp; Sustainability compliance' is Out of Scope as per PRD_Scope_Rules. This is handled as a common requirement across all products and tracked via Extended Supporting Documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>35</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Program Management</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Highly Leveraged Development Approach: Leverage Watt-LE mech platform, Marconi-Hi product (Reddington ID), and solutions for rapid development and low investment.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Minimizes risk and cost while accelerating time-to-market.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Development schedule milestones met with reuse of major components.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a development best practice/approach, not a product-specific feature or performance metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Program Management, Business Leadership</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schedule Constraint – High Priority: Maintain schedule as the least flexible constraint for the program, with defined checkpoints and milestones.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>On-time delivery is critical for market competitiveness and financial targets.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>All critical milestones met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a program management constraint, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization: Optimize schedule for Platform as a Service (PaaS) offering.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Aligns product launch with business model rollout.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PaaS available at launch and validated with initial customers.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to project scheduling, not a customer-facing product feature or improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PDL SKU Features: For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Violated: PRD Scope Rule. Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel), which is out of scope and should be managed via the extended supporting document process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization: Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Technical and business model enablement for monetization of AI and management solutions.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a business/strategic goal (monetization) rather than a product-specific feature. Should be routed to the correct forum for business planning.</t>
         </is>
       </c>
     </row>
@@ -876,7 +7926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,7 +8012,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -977,47 +8027,245 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Media Support</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer able to run all new/current EM / market segment media </t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Use EPS foam packaging for the new product.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Product must pass drop and vibration tests with EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures product safety during shipping and aligns with sustainability requirements (EPEAT3, LOT4, Blue Angel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Implement service station aerosol management and make necessary changes to the spit platform due to the new tank.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aerosol emissions must remain within HP and regulatory limits during operation.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Implement service station aerosol management.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reduces contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Reliability</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Printer able to run all new/current EM / market segment media </t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube configuration and increased weights.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Carriage must operate within designed force limits and pass reliability tests with new configuration.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Updated carriage dynamic and force models.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,476 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Implement new NGB keyed bottles with a page yield of 6,000 for black and 6,000 for CMY, and bottle size for CMY greater than 8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The printer must accept new NGB keyed bottles and achieve at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Achieve 6,000 pages for black and CMY, and CMY bottle size supports &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>High page yield bottles reduce frequency of replacement, enhance customer convenience, and align with market expectations for CISS printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Design the ink bottle and tank interface to ensure spill-free reliability during user refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spillage observed in 100 consecutive refill cycles under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents mess and improves user experience, critical for consumer and SMB segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units must pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units pass tamper evidence and sealing tests as per HP standards.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances security, tamper evidence, and product integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The new printer must operate reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The new printer operates reliably using existing SuperAmp Si PHA and Magi/Nessie inks without any reformulation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, speeds time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Support for Service Parts and Warranty: NOA-F must be available as a service part for in-warranty support, and the system must support customer-replaceable PHA and NOA-F.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA must be replaceable by customers or service centers, and available as service parts within warranty period.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F and PHA are customer-replaceable and available as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime for end users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature on the bottle lid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All bottles must have Acumen 6 feature validated in production samples.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All bottles have validated Acumen 6 feature on the lid.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Supports authentication and anti-counterfeit measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leverage Watt LE / Marconi Hi Mech + CISS: Leverage existing Watt LE and Marconi Hi mechanical platforms, integrating with CISS for the new product.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>New product must pass all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Product passes all system integration tests with Watt LE/Marconi Hi base and CISS.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces development time and investment by building on proven platforms.</t>
         </is>
       </c>
     </row>
@@ -592,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,6 +1344,138 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold/Target is not specific. 'Meet customer requirement' is too vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F: Modify existing SA14 production line to accommodate NOA-F requirements, and add Magi ink cart and labeling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new product configurations.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Production lines must be validated and able to produce new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Validated production lines capable of producing new configurations at planned capacity.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal operational process, not a customer-facing product feature. To be handled in Ops readiness forum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>New Keyed Caps Mold Tooling: Invest in mold tooling for 1 to 4 new keyed bottle caps.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Supports differentiation and compatibility control for new bottle types.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Mold tools must be delivered and pass first article inspection for all new cap designs.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Mold tools for 1-4 new keyed caps delivered and pass first article inspection.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal capex/tooling item, not a customer-facing product feature. The resulting feature (keyed cap) is in scope, but the tooling is not.</t>
         </is>
       </c>
     </row>
@@ -888,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1632,72 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Enhanced Reliability and Ink Stability Modeling: Perform comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life scenarios. Model ink stability in tank and its impact on print quality.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Reliability and stability models must predict at least 95% uptime and consistent PQ (Print Quality) over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Models predict at least 95% uptime and consistent PQ over 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures consistent performance, longevity, and print quality throughout product life.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,472 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>The requirement focuses on a customer-facing improvement (reducing confusion in OOBE) and provides specific, measurable targets (reducing multiple names to one or two), aligning with the redefine guidelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Wong, Rahul1 Shin, Rahul1 Lim, Rahul1 Ming, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong, Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Implement a user-replaceable maintenance box.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Shin, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Key printer components are customer-replaceable (PHA); MINK parts are serviceable at authorized centers; most parts are customer-replaceable out of warranty.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Utilize keyed ink bottles to prevent incorrect refilling.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
         </is>
       </c>
     </row>
@@ -588,9 +1054,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Channel requests for warranty improvements to the appropriate function owners (Marketing, GxD, TME) for holistic assessment.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -601,7 +1206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,6 +1558,142 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>This requirement describes a hardware reliability test. According to the PRD_Scope_Rules, such common reliability requirements are handled as extended supporting documents, not as in-scope PRD items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim, Rahul1 Ming, Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PDL SKU with 25/20 ppm speed, PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming, Rahul1, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm at least 60% recycled content plastic (RCP); verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Manufacture with at least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,872 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Wong, Rahul1 Shin, Rahul1 Lim, Rahul1 Ming, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Achieve HP’s lowest total cost of ownership (TCO) for business customers.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong, Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A user-replaceable maintenance box is implemented.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Shin, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Key printer components are customer-replaceable (PHA); most MINK parts are customer-replaceable out of warranty.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first).</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU includes SMB2.0 Solutions and an Advanced View SMB Portal.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Lim, Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Speed, Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PDL SKU has print speed of 25/20 ppm, PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GXD, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Manageability: Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AI Solutions: Print, Scan, Support: Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS: Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GXD, Marketing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
         </is>
       </c>
     </row>
@@ -802,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +1883,72 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Ming, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Manufacture with at least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,872 +562,6 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Parvin, Rahul1 Wong, Rahul1 Shin, Rahul1 Lim, Rahul1 Ming, Rahul1 Hui</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Wong</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CPP</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Achieve HP’s lowest total cost of ownership (TCO) for business customers.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Go to market</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Wong, Rahul1 Shin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>A user-replaceable maintenance box is implemented.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Shin, Rahul1 Lim</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>['Quality', 'DVAR', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Key printer components are customer-replaceable (PHA); most MINK parts are customer-replaceable out of warranty.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Wong</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>All ink bottles are keyed and only fit correct tanks.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>['Quality', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Warranty Improvement</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Durability</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first).</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Parvin, Rahul1 Hui</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU includes SMB2.0 Solutions and an Advanced View SMB Portal.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Lim, Rahul1 Ming</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Print Speed, Environmental Ecolabel</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PDL SKU</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>PDL SKU has print speed of 25/20 ppm, PDL/PS support, and Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Hui</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GXD, BA, Marketing</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Consolidated SMB Portal for Manageability: Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, GXD, BA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>AI Solutions: Print, Scan, Support: Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AI features are functional and validated in real-world SMB environments.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>AI features are functional and validated in real-world SMB environments.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Hui</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Marketing, BA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Platform Support for PaaS: Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PaaS features are available and operational in production units.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>PaaS features are available and operational in production units.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GXD, Marketing</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Connectivity</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,72 +1014,6 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1, Rahul1 Ming, Rahul1 Lim</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Sustainability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Environmental Leadership</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Manufacture with at least 60% recycled content plastic (RCP).</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,1668 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Wong, Rahul1 Shin, Rahul1 Lim, Rahul1 Ming, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Achieve HP’s lowest total cost of ownership (TCO) for business customers.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong, Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A user-replaceable maintenance box is implemented.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Shin, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Key printer components are customer-replaceable (PHA); most MINK parts are customer-replaceable out of warranty.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first).</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Parvin, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU includes SMB2.0 Solutions and an Advanced View SMB Portal.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Lim, Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Speed, Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PDL SKU has print speed of 25/20 ppm, PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GXD, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Manageability: Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AI Solutions: Print, Scan, Support: Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS: Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GXD, Marketing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Wong, Shin, Lim, Ming, Hui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>User testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Shin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Lim</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GXD, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Manageability: Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AI Solutions: Print, Scan, Support: Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS: Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GXD, Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
         </is>
       </c>
     </row>
@@ -802,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +2679,208 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Ming, Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Manufacture with at least 60% recycled content plastic (RCP).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1, Lim, Ming</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,872 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AI features are available and functional in production units.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>User testing confirms ease-of-use and workflow improvement.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO with Minimal Intervention: Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Achieve HP's lowest TCO for business customers with extended maintenance intervals.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First Business Ink Tank Printer for SMBs: Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Successfully launch and position the product as HP's first business ink tank printer.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box: Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maintenance box is customer-replaceable, verified by usability testing.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK): Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Documented list of customer-replaceable parts is available and verified.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Key components are customer-replaceable, verified by service and user testing.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Keyed ink bottle system prevents mis-filling and ensures reliability.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages or 2 years.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal: Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full portal and solutions functionality is verified and available on the Non-PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PDL SKU: Speed and Protocol Support: Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed (25/20 ppm), protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GXD, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal for Manageability: Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, BA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AI Solutions: Print, Scan, Support: Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AI features are functional and validated in real-world SMB environments.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS: Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PaaS features are available and operational in production units.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GXD, Marketing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
         </is>
       </c>
     </row>
@@ -872,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +1883,72 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BOM and manufacturing process confirm 60% RCP.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Manufacture with at least 60% recycled content plastic (RCP), verified by sustainability audit.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,9 +415,2494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Wong, Shin, Lim, Ming, Hui</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions: Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AI-powered productivity, scan, and management features are available and verifiable in the product UI; features function as documented and pass UAT.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Advanced AI-powered productivity features, scan workflow automation, and manageability solutions are fully integrated and validated.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming, Hui</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Introduce a replaceable maintenance box that customers can easily swap without technical support, reducing downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions; no tools required; validated in usability testing.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions and no tools.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Utilize uniquely keyed ink bottles to prevent incorrect refilling and ensure compatibility, reducing user error and warranty claims.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ink bottles are physically keyed and only compatible with intended slots; verified in QA and field tests.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ink bottles are physically keyed and only compatible with intended slots.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management: Develop a consolidated SMB portal for managing multiple printers, targeting unmanaged or lightly managed SMBs without dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Portal is accessible, supports management of at least 15 printers, and passes security and usability tests.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A consolidated SMB portal that supports management of at least 15 printers.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Lim, Hui</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing, DVAR, Tech Reg, BA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) Support: Ensure Magellan is compatible with HP's PaaS offerings, enabling subscription-based services and remote management features.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Magellan can be provisioned, managed, and monitored via HP PaaS platform; validated in integration testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full compatibility with HP PaaS platform for provisioning, management, and monitoring.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Lim, Hui</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Tech Reg, BA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PDL/PS Support for PDL SKU: Provide full PDL (Page Description Language) and PostScript support for the PDL SKU, with print speeds of 25/20 ppm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm in standardized print tests; PDL/PS compatibility validated with common business software.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>25/20 ppm print speed for PDL SKU with full PDL/PS support.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>80k/2 Year Warranty: Offer a warranty of 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Warranty terms of 80,000 pages or 2 years are published and supported; warranty claims tracked for compliance.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A warranty of 80,000 pages or 2 years (whichever comes first).</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Ming</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Serviceability: PHA and MINK: Enable customer-replaceable PHA components and MINK at service centers, with a target of making MINK customer-replaceable if out of warranty.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PHA components are customer-replaceable. MINK is replaceable at service centers. Validated in field trials per service guide.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Customer-replaceable PHA. MINK replaceable at service centers, with a goal for customer-replacement out of warranty.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan AI Solutions: Integrate advanced AI algorithms for print and scan quality enhancement, ensuring optimal output with minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AI features demonstrably improve print/scan quality in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>User satisfaction &gt;90% in surveys.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App: Support mobile printing workflows through the HP App, enabling users to print from smartphones and tablets.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Lim, Hui</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, Tech Reg, BA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Advanced Telemetry Requirements: Implement telemetry features for remote diagnostics, usage tracking, and predictive maintenance, aligned with HP enterprise standards.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Telemetry data is available in the SMB portal and HP support tools; GDPR compliance verified.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Telemetry data is available in the SMB portal and HP support tools.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield; CMY bottle size must support &gt;8K pages.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bottles must be able to deliver at least 6,000 pages (Black/CMY) as validated by standardized yield tests.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CMY bottle size must support &gt;8,000 pages as validated by standardized yield tests.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quality, Customer Support</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new ink bottles and tank system deliver spill-free reliability during user refill and maintenance operations.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Less than 1% of user refill events result in ink spills, as measured in field trials and lab tests.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Less than 1% of user refill events result in ink spills.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Security</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Security</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F (Non-OEM Accessory-Filter) with a metal foiled labyrinth and lid label. No changes to click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NOA-F units must pass reliability and security tests with the new labyrinth and label, and be compatible with existing mechanisms.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NOA-F units pass all reliability and security tests.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts in Warranty Support: NOA-F must be available as service parts for warranty support and field replacements.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology onto the ink bottle lid for authentication or tracking.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Improves anti-counterfeiting and supply chain traceability.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Improves anti-counterfeiting and supply chain traceability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Modify Factory Line for NOA-F and New Bottles: Modify SA14 production line for NOA-F assembly; add Magi ink cart and labeling tool in Orcus 5. Mold for 1-4 new keyed caps required.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Supports manufacturing of new consumables and assemblies.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Supports manufacturing of new consumables and assemblies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Support Customer-Replaceable PHA and NOA-F: Design the system to allow customers to easily replace PHA (Printhead Assembly) and NOA-F without professional service.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Replacement process can be performed by end users in under 5 minutes with no tools, as validated in usability studies.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Replacement process can be performed by end users in under 5 minutes with no tools.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DerivativeID</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington ID with a size increase for the ink tank. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging: Utilize EPS foam packaging for the printer and consumables.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Protects product during shipping and handling.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Products pass drop and vibration tests with EPS packaging.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Products pass drop and vibration tests with EPS packaging.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Protects product during shipping and handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications for Tank Protrusion: Modify input and output trays to align with the increased tank protrusion.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and usability.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and usability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Size Optimization of Printer: Optimize overall printer size, considering the increased tank and new components.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Final product dimensions do not exceed agreed size envelope and pass ergonomic review.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Final product dimensions do not exceed agreed size envelope.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration: Integrate a 4.3” CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Improves user experience and modernizes product appearance.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Display is fully functional and passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Display is fully functional and passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Improves user experience and modernizes product appearance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with Sayan Sibstar Tubes and New Routing: Leverage Sayan Sibstar tubes, introduce new tube routing and integration for the 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Supports new ink system architecture and reliability.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Supports new ink system architecture and reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paper Path Support for Increased Page Life: Redesign paper path to support increased page life (80K pages).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability for higher duty cycles.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Paper path components pass 80K page accelerated wear tests.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Paper path components pass 80K page accelerated wear tests.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability for higher duty cycles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>140ml K and XXml CMY Bottles: Introduce new 140ml Black (K) bottles and appropriately sized CMY bottles for the new system.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Aligns with increased yield and system design.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Aligns with increased yield and system design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>New Make-Break and FI Connection for IDS: Develop new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System).</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of the ink system.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>New connection passes leak, durability, and usability tests.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>New connection passes leak, durability, and usability tests.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of the ink system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank: Increase LEBI (Low-End Bulk Ink) ink-tank size, implement new keying, and integrate LOI (Level of Integration) with one SHAID (Security Hardware Authentication ID).</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Tank passes installation, capacity, and security validation tests.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tank passes installation, capacity, and security validation tests.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop a new IDS startup algorithm and air management system for reliable operation.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and prevents air entrapment issues.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and prevents air entrapment issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Engineering, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi, Dune FW: Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new printer.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>All reused components function as required in system integration tests.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>All reused components function as required in system integration tests.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven, reliable components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Product Security, IT, End Users</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW): Integrate Gauss4.xx hardware and firmware security features into the printer.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Protects product and user data from security threats.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external penetration testing.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external penetration testing.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Protects product and user data from security threats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>standard, PDL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Speed: 25/20 ppm (PDL: 25/19 ppm): Printer must support print speeds of 25/20 pages per minute (ppm) for standard and 25/19 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and competitiveness.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25/19 ppm for PDL SKU. Printer achieves required speeds in standardized performance tests.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25/20 ppm for standard SKU, 25/19 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and competitiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box: Design printer with a serviceable maintenance box for easy end-user or service center replacement.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces repair costs.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces repair costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K: Support hosting of 12K-CMYK and trade page yield of 6K as flexible business requirements.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Provides flexibility for different market segments and promotions.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Printer supports 12K-CMYK and 6K trade page configurations as validated in market trials.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Printer supports 12K-CMYK and 6K trade page configurations.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Provides flexibility for different market segments and promotions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Enterprise IT, SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Solution and Services Integration: Scan, Manageability, Enterprise Support: Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM, JAM.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>All solution features are functional and validated in enterprise and SMB pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Full functional integration with WJA, HPSM, JAM and other specified solutions.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>End Users, IT, Support</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD: Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Maximizes compatibility and ease of use for customers across segments.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Maximizes compatibility and ease of use for customers across segments.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -428,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +3270,472 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Violated: Redefine Guideline - Threshold and Target ('Meet customer requirement') are not specific or measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Hui</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO (Total Cost of Ownership): Design Magellan to deliver the lowest total cost of ownership for SMBs among HP business printers, including minimal intervention and optimized consumables.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>To attract cost-conscious SMBs and compete effectively in the CISS PLE Hi segment.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TCO calculations demonstrate lower ownership costs than previous HP models and key competitors in third-party benchmarks.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Lowest TCO among HP business printers and key competitors in the segment.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement threshold references predecessor ('lower ownership costs than previous HP models'). Requirements must be defined with specific, measurable targets independent of predecessors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Engineering, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Engineering, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment ink without reformulation.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, accelerates time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>100% compatibility of reused components in prototype and pilot production builds.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>100% compatibility of reused components.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal engineering/implementation detail, not a customer-facing requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling and PQ Impact Analysis: Model ink stability in the tank and analyze its impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Maintains high print quality and reduces risk of ink degradation over time.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Documented ink stability model and PQ impact report reviewed and approved by R&amp;D.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Documented ink stability model and PQ impact report.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement describes an internal engineering analysis/process, not a measurable, customer-facing product feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force models to account for new tube routing and weights.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a general engineering process, not a customer-facing product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm: Implement new servicing and startup algorithms for improved reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Reduces errors and improves printer uptime.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold references 'previous generation'. Requirement thresholds and targets must be specific, measurable, and must not reference 'Equal or better than Predecessor'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>New PQ Goals and Depletion Definition: Establish new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations and marketing claims.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement thresholds and targets must be specific, measurable. The acceptance criteria describes a process for approval rather than a measurable target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Business Development, SMB Customers, IT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SMB Solution and PaaS Support: Support SMB solution features and Printer-as-a-Service (PaaS) business models.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports new revenue streams.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold is not specific. 'as required by business model' is not a measurable criterion.</t>
         </is>
       </c>
     </row>
@@ -799,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,6 +3895,410 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification: Achieve Blue Angel environmental certification for the PDL SKU, demonstrating commitment to sustainability and eco-friendly design.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Certification is obtained and documented prior to launch.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Achieve Blue Angel environmental certification for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1, Ming</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prod Steward, Quality, Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% RCP Content: Ensure Magellan is manufactured with at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Product Bill of Materials demonstrates 60% RCP.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>60% RCP verified by third-party audit.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ink System Reliability and Characterization: Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Validated models and test data for all key reliability metrics before design freeze.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Validated models and test data for all key reliability metrics.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>New Warranty Page Life Goal: 80K Pages: Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Printer must reliably print 80,000 pages without major failure, as verified in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Printer must reliably print 80,000 pages without major failure.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environment &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU: Ensure compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Environmental - Compliance</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Update service station for aerosol management with spit platform changes due to new tank design.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prevents contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prevents contamination and maintains print quality.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,2862 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield: Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Black yields 6,000 pages, CMY bottles are &gt;8,000-page size.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Bottle Reliability: Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>To enhance reliability and maintain established user experience features.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>To enhance reliability and maintain established user experience features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No reformulation required for SuperAmp Si PHA and Magi/Nessie ink.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts in Warranty Support: NOA-F units must be available as service parts for warranty support.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 feature into the printer lid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>To support advanced features or security as per platform standards.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is operational and tested on the production lid.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is operational and tested on the production lid.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>To support advanced features or security as per platform standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart: Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>To enable efficient manufacturing of the new printer and consumables.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>To enable efficient manufacturing of the new printer and consumables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>To improve user serviceability and reduce support costs.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Users can replace PHA and NOA-F without tools in under 5 minutes.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>To improve user serviceability and reduce support costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80k Pages: Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>To meet market expectations for durability and reduce warranty claims.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>80,000 pages warranty page life.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>To meet market expectations for durability and reduce warranty claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size: Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>To support higher ink capacity while maintaining design identity.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tank size increased as per spec, Reddington ID is maintained.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>To support higher ink capacity while maintaining design identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion: Modify input and output trays to align with increased tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration: Integrate a 4.3-inch CGD display into the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>To provide a modern and user-friendly interface.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>To provide a modern and user-friendly interface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with New Tube Routing and Integration: Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>To improve ink delivery and system reliability.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>To improve ink delivery and system reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management: Update service station for aerosol management with spit platform changes due to new tank.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>To ensure proper aerosol handling and maintain print quality.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>To ensure proper aerosol handling and maintain print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part Post-80k Life: Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>To extend printer service life and reduce total cost of ownership.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>To extend printer service life and reduce total cost of ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>140ml Black Bottles and New CMY Bottle Sizes: Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>To support higher print volumes and reduce refill frequency.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>To support higher print volumes and reduce refill frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Implement a new IDS startup algorithm and air management system for Magellan.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>To optimize ink delivery system performance and startup reliability.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>To optimize ink delivery system performance and startup reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>To leverage proven electronics and reduce development cost and risk.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>All reused components operate to spec in Magellan printer.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>All reused components operate to spec in Magellan printer.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>To leverage proven electronics and reduce development cost and risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wifi</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration: Integrate Stingray Wi-Fi module into Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>To provide wireless connectivity as per current standards.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>To provide wireless connectivity as per current standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>FW Dune and Gauss4.xx Security Integration: Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>To ensure security compliance and protect user data.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>To ensure security compliance and protect user data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Business Model Support for Consumer, SMB, and Enterprise: Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>To maximize market reach and adapt to diverse customer needs.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>To maximize market reach and adapt to diverse customer needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support: Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>To enhance solution offering and address business customer requirements.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>To enhance solution offering and address business customer requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>28</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD: Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>29</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Leverage Watt-LE/Marconi Hi Mech + CISS: Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>32</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years as Optimized Priority: Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>To align with market expectations and business priorities.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>To align with market expectations and business priorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority: Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>To meet performance requirements and market competitiveness.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>To meet performance requirements and market competitiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>34</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Serviceability of Maintenance Box as Optimized Priority: Design Magellan printer for easy servicing of the maintenance box.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>To improve post-sale support and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>To improve post-sale support and reduce downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>35</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SMB Solution Support as Optimized Priority: Magellan must support SMB solutions as an optimized business priority.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>To ensure the printer meets the needs of small and medium business customers.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SMB solutions are available and functional for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SMB solutions are available and functional for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>To ensure the printer meets the needs of small and medium business customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>36</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PaaS Schedule as Optimized Priority: Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>To support new business models and revenue streams.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>To support new business models and revenue streams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>37</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK as Flexible Priority: Provide support for hosting 12K-CMYK as a flexible business priority.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>To allow for future scalability and market adaptation.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>To allow for future scalability and market adaptation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>38</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Trade page 6K SKU</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Trade Page 6K as Flexible Priority: Support trade page 6K as a flexible business priority.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>To provide options for market-specific or promotional SKUs.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Trade page 6K option is available as a configurable SKU.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Trade page 6K option is available as a configurable SKU.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>To provide options for market-specific or promotional SKUs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>AI Productivity Solutions: Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Consolidated SMB Portal: Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO): Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Maintenance Box: Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Ink Refill: Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Keyed bottles are only compatible with correct tank.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years: Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Warranty covers 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Warranty covers 80,000 pages or 2 years, whichever comes first, supported by reliability testing.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Serviceability – PHA and MINK: Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PHA parts are customer-replaceable; MINK service available at authorized centers.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>non-PDL SKUs</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal: Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>13</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>eligible SKUs</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PaaS Enablement: Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin, Rahul1, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements: Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
         </is>
       </c>
     </row>
@@ -580,9 +3436,424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update: Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>To ensure reliable operation and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is a general engineering process standard, not a customer-facing improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm: Develop new servicing and startup algorithm for Magellan printer.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To improve reliability and user experience during initial setup and servicing.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Functional and experience improvements require clear, quantifiable metrics. The acceptance criteria 'passes reliability and usability testing' lacks a specific, measurable target/threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Others (To Be classified)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schedule as Least Flexible Constraint: Meet the schedule as the highest business constraint for Magellan program.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>To ensure timely market entry and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>All program milestones are met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>All program milestones are met as per published schedule.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Do not include best practices or general engineering/process standards. This is a program management constraint, not a product requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification: PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Requirement includes 'Blue Angel certification' which falls under the 'Environment &amp; Sustainability compliance' category, defined as Out of Scope in PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan Features: Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Acceptance Criteria lacks specific, measurable metrics. 'Defined benchmarks' must be specified within the requirement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +3864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +4219,344 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ming</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Certification: Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>To comply with environmental regulations and market requirements.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>To comply with environmental regulations and market requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paper Path Durability for Increased Page Life: Enhance paper path to support increased page life of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>To ensure printer reliability over its extended life expectancy.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>To ensure printer reliability over its extended life expectancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint: SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>To ensure reliability and meet business constraints for consumable life.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>To ensure reliability and meet business constraints for consumable life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1 Ming</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prod Steward</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP): Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>At least 60% RCP in product materials confirmed by third-party audit.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>At least 60% RCP in product materials.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim, Rahul1 Ming, Rahul1 Hui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Safety &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Advanced Security and Compliance: Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,484 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>The requirement is for a customer-facing improvement with a clear, measurable goal (reducing multiple product names to one) and a defined threshold (two names), which aligns with the redefine guidelines. The justification highlights that having too many names is inefficient and can induce user errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield: Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances air management, reliability, and product differentiation.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances air management, reliability, and product differentiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magellan, SuperAmp Si PHA, Magi/Nessie ink</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Prevents degradation of print quality and supports warranty claims.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Prevents degradation of print quality and supports warranty claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PHA, NOA-F</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces service costs and increases customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces service costs and increases customer satisfaction.</t>
         </is>
       </c>
     </row>
@@ -588,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,6 +1348,146 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Category 'HW Reliability' is out of scope and managed via an extended supporting document. Additionally, the Threshold/Target 'Meet customer requirement' is not specific or measurable, violating the Redefine Guidelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Modify Existing SA 14 Line for NOA-F: Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enables efficient manufacturing and quality control for new components.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing product requirement. Similar to 'Design for Manufacturing' examples listed as out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magi Ink</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5: Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Supports production of new ink system and traceability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process/tooling setup, not a customer-facing product requirement. Similar to 'Design for Manufacturing' and 'Test Setup / Fixture' examples listed as out of scope.</t>
         </is>
       </c>
     </row>
@@ -884,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1644,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>This requirement falls under Hardware Reliability, which is governed by a separate, standardized document as per the redefine rules. The business purpose is to ensure the printer meets intervention specifications for different media and climatic conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IDS, NOA-F</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Reliability and IDS Characterization &amp; Modeling: Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,76 +415,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -513,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>GXD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Out-of-Box Experience (OOBE) at 123.hp.com should present only one consistent printer reference name to the customer for HP OfficeJet Pro 9010 series, reducing the current four references to just one.</t>
+          <t>OOBE - reduce number of steps : 123.hp.com :</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -573,485 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The requirement is for a customer-facing improvement with a clear, measurable goal (reducing multiple product names to one) and a defined threshold (two names), which aligns with the redefine guidelines. The justification highlights that having too many names is inefficient and can induce user errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NGB</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield: Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GXD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Customer Experience</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spill-Free Reliability for Ink Bottles: Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GXD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Enhances air management, reliability, and product differentiation.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Enhances air management, reliability, and product differentiation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cost Reduction</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Magellan, SuperAmp Si PHA, Magi/Nessie ink</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Prevents degradation of print quality and supports warranty claims.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Prevents degradation of print quality and supports warranty claims.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Acumen 6 on Lid: Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PHA, NOA-F</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Support Customer Replaceable PHA and NOA-F: Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
+          <t>Having too many names for the same reference isn't efficient and can induce user errors.</t>
         </is>
       </c>
     </row>
@@ -1066,76 +576,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -1152,7 +662,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1177,7 +687,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The product must operate correctly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or similar failures.</t>
+          <t xml:space="preserve">Product can be placed and work on uneven surface ( sofa , table cloth , carpet …) </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1222,7 +732,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1247,7 +757,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The printer must be able to function without failure if tilted left or right up to 20 degrees during printing.</t>
+          <t>Tilt left and right each while printing</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1292,7 +802,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1307,7 +817,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>robustness</t>
+          <t>Print Quality</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1317,7 +827,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and function correctly when placed on a moving trolley during operation.</t>
+          <t>Put printer on trolley and print</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1348,146 +858,6 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Category 'HW Reliability' is out of scope and managed via an extended supporting document. Additionally, the Threshold/Target 'Meet customer requirement' is not specific or measurable, violating the Redefine Guidelines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Modify Existing SA 14 Line for NOA-F: Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Enables efficient manufacturing and quality control for new components.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing product requirement. Similar to 'Design for Manufacturing' examples listed as out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Magi Ink</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5: Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Supports production of new ink system and traceability.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process/tooling setup, not a customer-facing product requirement. Similar to 'Design for Manufacturing' and 'Test Setup / Fixture' examples listed as out of scope.</t>
         </is>
       </c>
     </row>
@@ -1502,76 +872,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -1588,7 +958,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HDRV</t>
+          <t>DVAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1603,7 +973,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Media Support</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1613,7 +983,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and media types for each market segment, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+          <t xml:space="preserve">Printer able to run all new/current EM / market segment media </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1643,77 +1013,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This requirement falls under Hardware Reliability, which is governed by a separate, standardized document as per the redefine rules. The business purpose is to ensure the printer meets intervention specifications for different media and climatic conditions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1 Shin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>IDS, NOA-F</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Reliability and IDS Characterization &amp; Modeling: Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,2492 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Having too many names for the same reference isn't efficient and can induce user errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NGB</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield: Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhances air management, reliability, and product differentiation.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enhances air management, reliability, and product differentiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magellan, SuperAmp Si PHA, Magi/Nessie ink</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink: Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Prevents degradation of print quality and supports warranty claims.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Prevents degradation of print quality and supports warranty claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PHA, NOA-F</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Reduces service costs and increases customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Reduces service costs and increases customer satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Changes for Tank Protrusion: Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Redesigned trays that accommodate tank protrusion and meet target dimensions.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display: Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Improves usability and aligns with market expectations for modern printers.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Display is functional and passes user experience testing.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Functional 4.3-inch CGD that passes UX testing.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Improves usability and aligns with market expectations for modern printers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model with New Tubes and Weights: Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ensures print quality and mechanical reliability.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Carriage operates within force and acceleration limits.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Ensures print quality and mechanical reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life): Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Facilitates extended product life and supports service contracts.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Serviceable ink maintenance parts, replaceable in &lt;30 minutes.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Facilitates extended product life and supports service contracts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rahul1 Wong</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Magellan platform</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>140ml Black and New CMY Bottles: Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bottles meet capacity and compatibility requirements in production units.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>140ml black bottles and new capacity CMY bottles.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Supports higher page yields and reduces refill frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>New IDS Make-Break and FI Connection: Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of ink connections.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of ink connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Wong</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Security, Supply Chain</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leverage LEBI Ink-Tank with Increased Size and Keying: Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Prevents cross-contamination and supports secure supply chain.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Prevents cross-contamination and supports secure supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management: Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm: Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Improves system uptime and reduces service calls.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Improves system uptime and reduces service calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marketing, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>New PQ Goals and Depletion Definition: Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>28</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Supply Chain</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU: Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module and Dune Firmware: Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Security, R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW): Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ensures compliance with security standards and protects against threats.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ensures compliance with security standards and protects against threats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>31</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BA, Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Go to market</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Support for Consumer, SMB, and Enterprise Segments: Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Expands market reach and supports diverse customer requirements.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Expands market reach and supports diverse customer requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM): Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>33</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Support for Multiple Clients and Drivers: Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Product Management, Service, End Users</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Product Management, Service</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or 80k Pages: Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2 years or 80,000 pages warranty</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Aligns with customer expectations and competitive offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>36</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PDL SKUs</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM): Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Meets market performance benchmarks and customer needs.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Printer achieves specified throughput in ISO test conditions.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25/20 PPM (PDL: 25/19 PPM)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Meets market performance benchmarks and customer needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Service, Product Management</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Serviceability of Maintenance Box: Ensure maintenance box is easily serviceable for users or service technicians.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>&lt;10 minutes replacement time</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Magellan printer</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions: Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Reduce management time by at least 30%.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui, Wong</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing, BA, Quality, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Magellan</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO for SMB Segment: Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Lowest TCO in its class; maintenance intervals &gt;20% longer than previous models.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Hui</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box: Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>80% of replacements can be performed by end-users without assistance.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Hui, Lim</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles: Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>100% prevention of incorrect bottle insertion.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui, Shin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management: Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Portal supports management of at least 15 devices with actionable alerts.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rahul1, Shin, Hui</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU): Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Hui</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan AI Solutions: Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>At least 20% improvement in output quality and ease of use over previous models.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rahul1, Ming, Lim</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Tech Reg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Environmental Leadership</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP): Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>At least 60% RCP.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rahul1, Wong, Hui</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Minimal Maintenance Design: Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Reduces operational costs and downtime for SMBs.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>At least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Reduces operational costs and downtime for SMBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rahul1, Parvin, Shin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Telemetry</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Support Experience</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Comprehensive Telemetry Support: Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Telemetry data is accessible via SMB portal and HP support tools and validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rahul1, Hui</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration: Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Printer is discoverable and manageable via HP App and passes mobile printing certification tests.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
         </is>
       </c>
     </row>
@@ -576,7 +3062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,6 +3344,352 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Violated: Category 'HW Reliability' is out of scope and managed via an extended supporting document. Additionally, the Threshold/Target 'Meet customer requirement' is not specific or measurable, violating the Redefine Guidelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Modify Existing SA 14 Line for NOA-F: Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enables efficient manufacturing and quality control for new components.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing product requirement. Similar to 'Design for Manufacturing' examples listed as out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Magi Ink</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5: Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Supports production of new ink system and traceability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process/tooling setup, not a customer-facing product requirement. Similar to 'Design for Manufacturing' and 'Test Setup / Fixture' examples listed as out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SuperAmp</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages: Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Critical for product reliability and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>65,000 pages</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope based on PRD_Scope_Rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product Management, Business</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Product Management, Business</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible): Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Allows adaptation to changing market and business needs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Configurations are validated and available as business needs arise.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Support host 12K-CMYK and trade page 6K configurations</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold is not specific or measurable ('available as business needs arise').</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1, Lim, Shin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing, Tech Reg, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Print Speed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PDL SKU Performance and Compatibility: PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ensures competitive performance and compliance for managed office environments.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves required print speeds (25/20 ppm), passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>25/20 ppm print speed, PDL/PS compatibility, Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Violated: Requirement includes 'Environment &amp; Sustainability compliance' (Blue Angel certification), which is defined as Out of Scope in PRD_Scope_Rules.</t>
         </is>
       </c>
     </row>
@@ -872,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +3849,344 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IDS, NOA-F</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Reliability and IDS Characterization &amp; Modeling: Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Support New Warranty Page Life Goal of 80k Pages: Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>80,000 pages page life</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1 Lim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU: Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Certification for EPEAT3, LOT4, and Blue Angel.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing: Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Improves reliability and supports new tank configuration.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Leak-free and flow-issue-free tube installation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Improves reliability and supports new tank configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paper Path Support for Increased Page Life: Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ensures consistent reliability and performance over extended use.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Paper path components pass 80k page accelerated life test.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>80k page life for paper path components.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Ensures consistent reliability and performance over extended use.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,468 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>This requirement focuses on improving the customer experience on 123.hp.com by reducing confusion caused by multiple product names for the same reference, which can lead to user errors. The goal is to streamline the naming to be more efficient and user-friendly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New NGB keyed ink bottles with 6K Black and &gt;8K CMY page yield.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Spill-free reliability with zero leakage in 99%+ of test cases.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units produced with metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Reuse existing Superamp Si PHA and Magi/Nessie inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOA-F is available as a service part for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PHA and NOA-F are customer replaceable without tools.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
     </row>
@@ -588,9 +1050,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Shin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Complete characterization and modeling reports for all specified parameters.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Category 'HW Reliability' is Out of Scope per PRD_Scope_Rules. This should be handled via the DVAR SharePoint as an extended supporting document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Model ink stability to demonstrate no significant PQ impact over the product lifecycle.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold 'no significant PQ impact' is not specific or measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Update and validate production lines for new components.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing improvement or visible touchpoint.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,468 +574,6 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>This requirement focuses on improving the customer experience on 123.hp.com by reducing confusion caused by multiple product names for the same reference, which can lead to user errors. The goal is to streamline the naming to be more efficient and user-friendly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Parvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>New NGB keyed ink bottles with 6K Black and &gt;8K CMY page yield.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Parvin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Spill-free reliability with zero leakage in 99%+ of test cases.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Parvin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>All NOA-F units produced with metal foiled labyrinth and lid label.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Parvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Reuse existing Superamp Si PHA and Magi/Nessie inks without reformulation.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NOA-F is available as a service part for in-warranty support.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Integrate Acumen 6 technology into the lid component.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>PHA and NOA-F are customer replaceable without tools.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
     </row>
@@ -1050,280 +588,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Shin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HW Reliability</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Complete characterization and modeling reports for all specified parameters.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>OUT_OF_SCOPE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Category 'HW Reliability' is Out of Scope per PRD_Scope_Rules. This should be handled via the DVAR SharePoint as an extended supporting document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Prevents ink degradation and maintains consistent print quality.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Model ink stability to demonstrate no significant PQ impact over the product lifecycle.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>OUT_OF_SCOPE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold 'no significant PQ impact' is not specific or measurable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Reduce factory complexity</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Update and validate production lines for new components.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>OUT_OF_SCOPE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing improvement or visible touchpoint.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,6 +574,426 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>This requirement focuses on improving the customer experience on 123.hp.com by reducing confusion caused by multiple product names for the same reference, which can lead to user errors. The goal is to streamline the naming to be more efficient and user-friendly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NGB keyed ink bottles</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NGB keyed bottles</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in 100% of test cases.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units produced with metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lid</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PHA, NOA-F</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
     </row>
@@ -588,9 +1008,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Superamp Si PHA, Magi/Nessie pigment inks</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Threshold must be specific and not reference 'Equal or better than Predecessor'. 'Without performance degradation' is a relative and non-specific metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no PQ impact.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Functional improvements require measurable metrics. 'No significant PQ impact' is subjective and not a measurable metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NOA-F, Magi ink cart, keyed caps</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal operational process (Design for Manufacturing), not a customer-facing improvement or visible touchpoint.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -601,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,6 +1652,76 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>Program Lead to insert one liner in PRD referencing the Reliability Requirement doc rev 1.x, with SharePoint link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,76 +415,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -513,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GXD</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -573,427 +561,11 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This requirement focuses on improving the customer experience on 123.hp.com by reducing confusion caused by multiple product names for the same reference, which can lead to user errors. The goal is to streamline the naming to be more efficient and user-friendly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NGB keyed ink bottles</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NGB keyed bottles</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in 100% of test cases.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>All NOA-F units produced with metal foiled labyrinth and lid label.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lid</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PHA, NOA-F</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
     </row>
@@ -1008,288 +580,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Cost Reduction</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Reduce factory complexity</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Superamp Si PHA, Magi/Nessie pigment inks</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Threshold must be specific and not reference 'Equal or better than Predecessor'. 'Without performance degradation' is a relative and non-specific metric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Prevents ink degradation and maintains consistent print quality.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no PQ impact.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Functional improvements require measurable metrics. 'No significant PQ impact' is subjective and not a measurable metric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NOA-F, Magi ink cart, keyed caps</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is an internal operational process (Design for Manufacturing), not a customer-facing improvement or visible touchpoint.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1300,76 +593,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
@@ -1386,7 +679,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1401,7 +694,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Media Support</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1441,7 +734,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Program Lead to insert one liner in PRD referencing the Reliability Requirement doc rev 1.x, with SharePoint link.</t>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
     </row>
@@ -1456,7 +749,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1471,7 +764,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Durability</t>
+          <t>robustness</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1511,7 +804,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Program Lead to insert one liner in PRD referencing the Reliability Requirement doc rev 1.x, with SharePoint link.</t>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
         </is>
       </c>
     </row>
@@ -1526,7 +819,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1581,7 +874,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Program Lead to insert one liner in PRD referencing the Reliability Requirement doc rev 1.x, with SharePoint link.</t>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
         </is>
       </c>
     </row>
@@ -1596,7 +889,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DVAR</t>
+          <t>HDRV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1651,77 +944,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Program Lead to insert one liner in PRD referencing the Reliability Requirement doc rev 1.x, with SharePoint link.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1 Shin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HW Reliability</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,426 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NGB keyed ink bottles</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New bottles demonstrate 6K Black and &gt;8K CMY page output.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NGB keyed bottles</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bottles pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NOA-F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>100% of NOA-F units are produced with metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lid component</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Warranty Improvement</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80K Pages: The printer must support a new warranty page life goal of 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>80,000 pages warranty page life.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
     </row>
@@ -580,9 +1000,292 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1 Parvin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>All new units</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Acceptance Criteria 'without performance degradation' is not specific and is equivalent to 'Equal or better than Predecessor'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Acceptance Criteria 'no significant PQ impact' is not specific or measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SA 14 line, Orcus 5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>outscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is related to internal manufacturing processes, not a customer-facing improvement or visible touchpoint. It is similar to out-of-scope examples for Design for Manufacturing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +1648,76 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,426 +566,6 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NGB keyed ink bottles</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>New bottles demonstrate 6K Black and &gt;8K CMY page output.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NGB keyed bottles</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bottles pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NOA-F</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100% of NOA-F units are produced with metal foiled labyrinth and lid label.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lid component</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Warranty Improvement</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Durability</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Warranty Page Life Goal of 80K Pages: The printer must support a new warranty page life goal of 80,000 pages.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>80,000 pages warranty page life.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>inscope</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
     </row>
@@ -1000,292 +580,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rahul1 Parvin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Cost Reduction</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Reduce factory complexity</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>All new units</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Acceptance Criteria 'without performance degradation' is not specific and is equivalent to 'Equal or better than Predecessor'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Prevents ink degradation and maintains consistent print quality.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Acceptance Criteria 'no significant PQ impact' is not specific or measurable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SA 14 line, Orcus 5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>outscope</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is related to internal manufacturing processes, not a customer-facing improvement or visible touchpoint. It is similar to out-of-scope examples for Design for Manufacturing.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1296,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1648,76 +945,6 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HW Reliability</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>extended supporting document</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,534 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black and 6K CMY page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and security of the ink delivery system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cost Reduction</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reduce factory complexity</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven components for reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
     </row>
@@ -580,9 +1108,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Design For Manufacturing</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing improvement or visible touchpoint.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -593,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +1615,72 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1 Shin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HW Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ensures long-term product reliability and performance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,534 +566,6 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Performance/Feature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HW Spec</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NGB Keyed Bottles with Increased Yield: Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black and 6K CMY page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Customer Experience</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Supplies Reliability</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Improves reliability and security of the ink delivery system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cost Reduction</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reduce factory complexity</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink: Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages proven components for reliability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Quality Improvement &amp; Serviceability</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Print Quality</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Ink Stability Modeling: Model ink stability in the tank and assess impact on print quality (PQ).</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Prevents ink degradation and maintains consistent print quality.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Prevents ink degradation and maintains consistent print quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>NOA-F as Service Parts for Warranty Support: Make NOA-F available as service parts for in-warranty support.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Acumen 6 on Lid: Integrate Acumen 6 technology into the lid component.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Supportability &amp; Serviciablity</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Serviceability</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Support Customer Replaceable PHA and NOA-F: Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>IN_SCOPE</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
     </row>
@@ -1108,148 +580,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Item No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Requestor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Requestor Function</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>SubCategory</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SKUs Applicable</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Requirement (What)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Justification (Why)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rahul1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Design For Manufacturing</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart: Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>OUT_OF_SCOPE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Violated: Redefine Guideline - Requirement is an internal manufacturing process, not a customer-facing improvement or visible touchpoint.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1260,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1612,72 +945,6 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rahul1 Shin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DVAR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HW Reliability</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Reliability and Performance Characterization: Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>EXTENDED_SUPPORTING_DOCUMENT</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
     </row>
